--- a/test/fixtures/files/Sara-Alert-Format-Invalid-Headers.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-Invalid-Headers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3C6CC0-3163-4547-83A0-AF69ED3B23E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41DD5D4-BE45-7947-B277-BFA37DF1AD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="394">
   <si>
     <t>First Name</t>
   </si>
@@ -1196,6 +1196,12 @@
   </si>
   <si>
     <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>Follow-Up Reason</t>
+  </si>
+  <si>
+    <t>Follow-Up Note</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CX12"/>
+  <dimension ref="A1:CZ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1650,9 +1656,11 @@
     <col min="100" max="100" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="101" max="101" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="102" max="102" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1950,8 +1958,14 @@
       <c r="CX1" t="s">
         <v>378</v>
       </c>
+      <c r="CY1" t="s">
+        <v>392</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>393</v>
+      </c>
     </row>
-    <row r="2" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -2244,7 +2258,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="3" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -2531,7 +2545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -2815,7 +2829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -3064,7 +3078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -3306,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>201</v>
       </c>
@@ -3543,7 +3557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>219</v>
       </c>
@@ -3806,7 +3820,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>238</v>
       </c>
@@ -4067,7 +4081,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>254</v>
       </c>
@@ -4327,7 +4341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>274</v>
       </c>
@@ -4554,7 +4568,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:102" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:104" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>296</v>
       </c>
